--- a/data/stx_xlsx/IMMUN.ST.xlsx
+++ b/data/stx_xlsx/IMMUN.ST.xlsx
@@ -7053,15 +7053,33 @@
       <c r="H39" s="18">
         <v>2.0</v>
       </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
+      <c r="I39" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="J39" s="18">
+        <v>0.07</v>
+      </c>
+      <c r="K39" s="18">
+        <v>0.13</v>
+      </c>
+      <c r="L39" s="18">
+        <v>0.18</v>
+      </c>
+      <c r="M39" s="18">
+        <v>0.25</v>
+      </c>
+      <c r="N39" s="18">
+        <v>0.32</v>
+      </c>
+      <c r="O39" s="18">
+        <v>0.09</v>
+      </c>
+      <c r="P39" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="Q39" s="18">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="16" t="s">
@@ -7088,15 +7106,6 @@
       <c r="H40" s="18">
         <v>2.06</v>
       </c>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="16" t="s">
